--- a/frontend/public/addItems_uploadFormat.xlsx
+++ b/frontend/public/addItems_uploadFormat.xlsx
@@ -90,7 +90,7 @@
         <scheme val="minor"/>
       </rPr>
       <t>: SAP_ID, TITLE, QUANTITY
-PREV_DUE_DATE should be less than NEXT_DUE_DATE</t>
+PREV_DUE_DATE should be lesser than NEXT_DUE_DATE</t>
     </r>
   </si>
 </sst>

--- a/frontend/public/addItems_uploadFormat.xlsx
+++ b/frontend/public/addItems_uploadFormat.xlsx
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>PART_NO</t>
+  </si>
   <si>
     <t>SAP_ID</t>
   </si>
@@ -35,18 +38,21 @@
     <t>TITLE</t>
   </si>
   <si>
+    <t>QUANTITY</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
     <t>CATEGORY</t>
   </si>
   <si>
+    <t>LOCATION</t>
+  </si>
+  <si>
     <t>CAPACITY</t>
   </si>
   <si>
-    <t xml:space="preserve">QUANTITY </t>
-  </si>
-  <si>
-    <t>DESCRIPTION</t>
-  </si>
-  <si>
     <t>CERTIFICATE_NO</t>
   </si>
   <si>
@@ -59,13 +65,13 @@
     <t>NEXT_DUE_DATE</t>
   </si>
   <si>
-    <t>LOCATION</t>
-  </si>
-  <si>
     <t>OWNER</t>
   </si>
   <si>
     <t>UMC</t>
+  </si>
+  <si>
+    <t>DATE_ADDED</t>
   </si>
   <si>
     <t>REMARKS</t>
@@ -89,7 +95,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: SAP_ID, TITLE, QUANTITY
+      <t>: TITLE, QUANTITY
 PREV_DUE_DATE should be lesser than NEXT_DUE_DATE</t>
     </r>
   </si>
@@ -131,6 +137,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -150,14 +164,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -316,18 +322,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.15"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -519,12 +525,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -651,7 +672,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -663,34 +684,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -775,12 +796,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
@@ -791,28 +812,31 @@
     <xf numFmtId="181" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1348,44 +1372,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultColWidth="8.79279279279279" defaultRowHeight="16.05"/>
   <cols>
-    <col min="1" max="1" width="8.18018018018018" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.38738738738739" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.6756756756757" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.6756756756757" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.7657657657658" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.3603603603604" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.954954954955" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.08108108108108" style="2" customWidth="1"/>
-    <col min="9" max="10" width="18.2612612612613" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11.1711711711712" style="2" customWidth="1"/>
-    <col min="12" max="12" width="8.78378378378378" style="2" customWidth="1"/>
-    <col min="13" max="13" width="6.08108108108108" style="2" customWidth="1"/>
-    <col min="14" max="14" width="10.5765765765766" style="2" customWidth="1"/>
-    <col min="15" max="15" width="3.58558558558559" customWidth="1"/>
-    <col min="16" max="16" width="4.99099099099099" customWidth="1"/>
-    <col min="17" max="17" width="15.1531531531532" customWidth="1"/>
+    <col min="1" max="1" width="10.4324324324324" customWidth="1"/>
+    <col min="2" max="5" width="10.4324324324324" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.4324324324324" style="3" customWidth="1"/>
+    <col min="7" max="9" width="10.4324324324324" style="2" customWidth="1"/>
+    <col min="10" max="11" width="10.4324324324324" style="4" customWidth="1"/>
+    <col min="12" max="15" width="10.4324324324324" style="2" customWidth="1"/>
+    <col min="16" max="16" width="10.4324324324324" customWidth="1"/>
+    <col min="17" max="17" width="4.99099099099099" customWidth="1"/>
+    <col min="18" max="18" width="15.1531531531532" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" ht="48.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="6" t="s">
@@ -1394,13 +1411,13 @@
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="6" t="s">
@@ -1412,108 +1429,114 @@
       <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="9"/>
-    </row>
-    <row r="2" spans="16:17">
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-    </row>
-    <row r="3" spans="16:17">
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-    </row>
-    <row r="4" spans="16:17">
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-    </row>
-    <row r="5" spans="16:17">
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-    </row>
-    <row r="6" spans="16:17">
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-    </row>
-    <row r="7" spans="16:17">
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-    </row>
-    <row r="8" spans="16:17">
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-    </row>
-    <row r="9" spans="16:17">
-      <c r="P9" s="9" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q9" s="9"/>
-    </row>
-    <row r="10" spans="16:17">
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-    </row>
-    <row r="11" spans="16:17">
-      <c r="P11" s="11" t="s">
+      <c r="Q1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="Q11" s="12"/>
-    </row>
-    <row r="12" spans="16:17">
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-    </row>
-    <row r="13" spans="16:17">
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-    </row>
-    <row r="14" spans="16:17">
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-    </row>
-    <row r="15" spans="16:17">
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-    </row>
-    <row r="16" spans="16:17">
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-    </row>
-    <row r="17" spans="16:17">
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-    </row>
-    <row r="18" spans="16:17">
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-    </row>
-    <row r="19" spans="16:17">
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-    </row>
-    <row r="20" spans="16:17">
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
-    </row>
-    <row r="21" spans="16:17">
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-    </row>
-    <row r="22" spans="16:17">
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-    </row>
-    <row r="23" spans="16:17">
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
+      <c r="R1" s="10"/>
+    </row>
+    <row r="2" spans="17:18">
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+    </row>
+    <row r="3" spans="17:18">
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+    </row>
+    <row r="4" spans="17:18">
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+    </row>
+    <row r="5" spans="17:18">
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+    </row>
+    <row r="6" spans="17:18">
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+    </row>
+    <row r="7" spans="17:18">
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+    </row>
+    <row r="8" spans="17:18">
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+    </row>
+    <row r="9" spans="17:18">
+      <c r="Q9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="R9" s="10"/>
+    </row>
+    <row r="10" spans="17:18">
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+    </row>
+    <row r="11" spans="17:18">
+      <c r="Q11" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="R11" s="13"/>
+    </row>
+    <row r="12" spans="17:18">
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+    </row>
+    <row r="13" spans="17:18">
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+    </row>
+    <row r="14" spans="17:18">
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+    </row>
+    <row r="15" spans="17:18">
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+    </row>
+    <row r="16" spans="17:18">
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+    </row>
+    <row r="17" spans="17:18">
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+    </row>
+    <row r="18" spans="17:18">
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+    </row>
+    <row r="19" spans="17:18">
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+    </row>
+    <row r="20" spans="17:18">
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+    </row>
+    <row r="21" spans="17:18">
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+    </row>
+    <row r="22" spans="17:18">
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+    </row>
+    <row r="23" spans="17:18">
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="P1:Q7"/>
-    <mergeCell ref="P9:Q10"/>
-    <mergeCell ref="P11:Q23"/>
+    <mergeCell ref="Q1:R7"/>
+    <mergeCell ref="Q9:R10"/>
+    <mergeCell ref="Q11:R23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
